--- a/docs/待核实线索.xlsx
+++ b/docs/待核实线索.xlsx
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,6 +104,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -885,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q300"/>
+  <dimension ref="A1:S300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -904,7 +905,7 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -983,12 +984,22 @@
           <t>骑手原话</t>
         </is>
       </c>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
+        <is>
+          <t>出处</t>
+        </is>
+      </c>
+      <c r="Q1" s="12" t="inlineStr">
+        <is>
+          <t>位置说明</t>
+        </is>
+      </c>
+      <c r="R1" s="11" t="inlineStr">
         <is>
           <t>线索出处（核实后删除本列）</t>
         </is>
       </c>
-      <c r="Q1" s="11" t="inlineStr">
+      <c r="S1" s="11" t="inlineStr">
         <is>
           <t>到现场要核实什么</t>
         </is>
@@ -1022,16 +1033,15 @@
           <t>骑手反映晚上 8 点就关门。</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" s="4" t="n"/>
       <c r="N2" s="5" t="n"/>
       <c r="O2" s="4" t="n"/>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>反馈问卷答卷 1 第 5 题</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>政通路上是否真有驿站？叫什么？实际开放时间？注意：答卷所说的“9 点”与示例点位一致，可能是把示例当真了</t>
         </is>
@@ -1073,12 +1083,12 @@
       <c r="I3" s="4" t="n"/>
       <c r="N3" s="5" t="n"/>
       <c r="O3" s="4" t="n"/>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>反馈问卷答卷 1 第 5 题</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>国定路上是否有换电柜？哪个品牌？排队情况。注意：示例点位里有“国定路附近的换电柜”，可能是把示例当真了</t>
         </is>
@@ -1120,12 +1130,12 @@
       <c r="I4" s="4" t="n"/>
       <c r="N4" s="5" t="n"/>
       <c r="O4" s="4" t="n"/>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>反馈问卷答卷 1 第 9 题</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>找到具体门店；当面问店员是否允许骑手接热水，能否用卫生间</t>
         </is>
@@ -1167,12 +1177,12 @@
       <c r="I5" s="4" t="n"/>
       <c r="N5" s="5" t="n"/>
       <c r="O5" s="4" t="n"/>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>反馈问卷答卷 5 第 9 题（非骑手填写）</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>具体位置；骑手穿工服、拿外卖能否进入，是否需要登记</t>
         </is>
@@ -1214,12 +1224,12 @@
       <c r="I6" s="4" t="n"/>
       <c r="N6" s="5" t="n"/>
       <c r="O6" s="4" t="n"/>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>反馈问卷答卷 1 第 10 题</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>具体是哪一侧的卸货通道；中午实地看一次，拍照（不拍车牌和人脸）</t>
         </is>
@@ -1253,16 +1263,15 @@
           <t>楼号混乱，导航只到小区门口，找楼要花很久。</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" s="4" t="n"/>
       <c r="N7" s="5" t="n"/>
       <c r="O7" s="4" t="n"/>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>反馈问卷答卷 2 第 10 题</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>是哪个小区；楼号怎么乱（有无楼栋指示牌）；回访时请骑手在地图上指一下</t>
         </is>
@@ -1304,12 +1313,12 @@
       <c r="I8" s="4" t="n"/>
       <c r="N8" s="5" t="n"/>
       <c r="O8" s="4" t="n"/>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>反馈问卷答卷 3 第 10 题</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="S8" s="4" t="inlineStr">
         <is>
           <t>具体是门口哪一段路；晚上和雨天各看一次</t>
         </is>
